--- a/sample/Sample_Fuel_Vehicle_Report_October_2026.xlsx
+++ b/sample/Sample_Fuel_Vehicle_Report_October_2026.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K58"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -491,7 +491,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>30 Oct 26</t>
+          <t>31 Oct 26</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06/10/26</t>
+          <t>01/10/26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>405531</t>
+          <t>763688</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>63.30L</t>
+          <t>22.47L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -613,25 +613,25 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>177.31</v>
+        <v>55.05</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>23.13</v>
+        <v>7.18</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>-3.55</v>
+        <v>-0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>173.76</v>
+        <v>55.05</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>151.1</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15/10/26</t>
+          <t>01/10/26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>024658</t>
+          <t>810767</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>83.50L</t>
+          <t>28.70L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -660,25 +660,25 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>234.79</v>
+        <v>70.31</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>30.62</v>
+        <v>9.17</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>-2.82</v>
+        <v>-0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>231.97</v>
+        <v>70.31</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>201.71</v>
+        <v>61.14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24/10/26</t>
+          <t>10/10/26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>177211</t>
+          <t>747883</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.40L</t>
+          <t>25.99L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -707,30 +707,30 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>65.09</v>
+        <v>63.68</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>8.49</v>
+        <v>8.31</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>-0.78</v>
+        <v>-1.27</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>64.31</v>
+        <v>62.41</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>55.92</v>
+        <v>54.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18/10/26</t>
+          <t>11/10/26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CARD FEE</t>
+          <t>SAMPLE FUEL STATION D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -738,326 +738,326 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>446746</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>21.95L</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="n">
-        <v>4.59</v>
+        <v>53.78</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.6</v>
+        <v>7.01</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>4.59</v>
+        <v>53.78</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>3.99</v>
+        <v>46.77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>19/10/26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>946001</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>19.44L</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>47.63</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>6.21</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>46.68</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>40.59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>27/10/26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION B</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>703707</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>26.41L</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>55.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>18/10/26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CARD FEE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>30/10/26</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>TRANSACTION FEES</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" s="6" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" s="6" t="n">
         <v>4.58</v>
       </c>
-      <c r="H12" s="6" t="n">
+      <c r="H15" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="I12" s="6" t="n">
+      <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="6" t="n">
+      <c r="J15" s="6" t="n">
         <v>4.58</v>
       </c>
-      <c r="K12" s="6" t="n">
+      <c r="K15" s="6" t="n">
         <v>3.98</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Sub Totals</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>486.36</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>63.44</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <v>-7.15</v>
-      </c>
-      <c r="J13" s="7" t="n">
-        <v>479.21</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>416.7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>364.32</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>47.52</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>360.81</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>313.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>REGISTRATION: TST102</t>
         </is>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>COST CENTRE:</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>CARD NO: 107919</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>DRIVER NAME:</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Supplier Name</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Odometer Reading</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Voucher Number</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>Original Price Incl GST</t>
         </is>
       </c>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>Discount Value Incl GST</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Total Incl GST &amp; Discount</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Total excl GST &amp; Incl Disc</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>06/10/26</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SAMPLE FUEL STATION A</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>062818</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>48.80L</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Unleaded</t>
-        </is>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>137.5</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>17.93</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>-1.65</v>
-      </c>
-      <c r="J17" s="6" t="n">
-        <v>135.85</v>
-      </c>
-      <c r="K17" s="6" t="n">
-        <v>118.13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>15/10/26</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SAMPLE FUEL STATION B</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>136623</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>24.60L</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Unleaded</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>69.04000000000001</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>9.01</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="J18" s="6" t="n">
-        <v>68.20999999999999</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>59.31</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>24/10/26</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SAMPLE FUEL STATION C</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>410940</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>65.90L</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Unleaded</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>185.42</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>24.19</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>-2.23</v>
-      </c>
-      <c r="J19" s="6" t="n">
-        <v>183.19</v>
-      </c>
-      <c r="K19" s="6" t="n">
-        <v>159.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18/10/26</t>
+          <t>02/10/26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CARD FEE</t>
+          <t>SAMPLE FUEL STATION A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1065,365 +1065,373 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>506539</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>21.49L</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
       <c r="G20" s="6" t="n">
-        <v>4.59</v>
+        <v>52.65</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.6</v>
+        <v>6.87</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>4.59</v>
+        <v>52.02</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>3.99</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>17/10/26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION B</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>360802</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>22.92L</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>48.83</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19/10/26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION C</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>362586</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>40.28L</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>98.69</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>85.81999999999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>27/10/26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>687959</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>26.30L</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>56.03</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18/10/26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CARD FEE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>30/10/26</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>TRANSACTION FEES</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" s="6" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" s="6" t="n">
         <v>4.58</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H25" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J25" s="6" t="n">
         <v>4.58</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K25" s="6" t="n">
         <v>3.98</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Sub Totals</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>401.13</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <v>-4.71</v>
-      </c>
-      <c r="J22" s="7" t="n">
-        <v>396.42</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>344.71</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="G26" s="7" t="n">
+        <v>281.1</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>280.47</v>
+      </c>
+      <c r="K26" s="7" t="n">
+        <v>243.88</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>REGISTRATION: TST103</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>COST CENTRE:</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>CARD NO: 115838</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>DRIVER NAME:</t>
         </is>
       </c>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Supplier Name</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Odometer Reading</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Voucher Number</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>Product</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>Original Price Incl GST</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>Discount Value Incl GST</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Total Incl GST &amp; Discount</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Total excl GST &amp; Incl Disc</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>06/10/26</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SAMPLE FUEL STATION A</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>085495</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>36.50L</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>104.22</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>102.97</v>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>89.54000000000001</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>15/10/26</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SAMPLE FUEL STATION B</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>577129</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>38.50L</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>107.53</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>14.03</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>-1.29</v>
-      </c>
-      <c r="J27" s="6" t="n">
-        <v>106.24</v>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>92.38</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>24/10/26</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SAMPLE FUEL STATION C</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>860077</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>50.60L</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>141.5</v>
-      </c>
-      <c r="K28" s="6" t="n">
-        <v>123.04</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>18/10/26</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>CARD FEE</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" s="6" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="6" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="K29" s="6" t="n">
-        <v>3.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30/10/26</t>
+          <t>07/10/26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TRANSACTION FEES</t>
+          <t>SAMPLE FUEL STATION A</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1431,146 +1439,234 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>738055</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>43.41L</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
       <c r="G30" s="6" t="n">
-        <v>4.58</v>
+        <v>121.11</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.6</v>
+        <v>15.8</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0</v>
+        <v>-1.45</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>4.58</v>
+        <v>119.66</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>3.98</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Sub Totals</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>362.42</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>47.28</v>
-      </c>
-      <c r="I31" s="7" t="n">
-        <v>-2.54</v>
-      </c>
-      <c r="J31" s="7" t="n">
-        <v>359.88</v>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>312.93</v>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>09/10/26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION B</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>310812</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>43.32L</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>120.86</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J31" s="6" t="n">
+        <v>120.86</v>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>105.1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13/10/26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION C</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>501266</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>60.47L</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>22.01</v>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J32" s="6" t="n">
+        <v>168.71</v>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>146.7</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>REGISTRATION: TST104</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>COST CENTRE:</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>CARD NO: 123757</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n"/>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>DRIVER NAME:</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>15/10/26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>502019</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>42.14L</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>117.57</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="I33" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J33" s="6" t="n">
+        <v>117.57</v>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>102.23</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>Supplier Name</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Odometer Reading</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Voucher Number</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Original Price Incl GST</t>
-        </is>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>GST</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>Discount Value Incl GST</t>
-        </is>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>Total Incl GST &amp; Discount</t>
-        </is>
-      </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>Total excl GST &amp; Incl Disc</t>
-        </is>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>21/10/26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>375711</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>43.21L</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>120.56</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>15.73</v>
+      </c>
+      <c r="I34" s="6" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="J34" s="6" t="n">
+        <v>119.11</v>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>103.57</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06/10/26</t>
+          <t>18/10/26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SAMPLE FUEL STATION A</t>
+          <t>CARD FEE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1578,326 +1674,326 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>292945</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>32.60L</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Unleaded</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" s="6" t="n">
-        <v>91.92</v>
+        <v>4.59</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>11.99</v>
+        <v>0.6</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>90.08</v>
+        <v>4.59</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>78.33</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>30/10/26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TRANSACTION FEES</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I36" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Sub Totals</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>657.98</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="J37" s="7" t="n">
+        <v>655.08</v>
+      </c>
+      <c r="K37" s="7" t="n">
+        <v>569.62</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRATION: TST104</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>COST CENTRE:</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>CARD NO: 123757</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>DRIVER NAME:</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Supplier Name</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Odometer Reading</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Voucher Number</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Original Price Incl GST</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Discount Value Incl GST</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Total Incl GST &amp; Discount</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Total excl GST &amp; Incl Disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>03/10/26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>532186</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>29.03L</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="I41" s="6" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="K41" s="6" t="n">
+        <v>61.1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14/10/26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION B</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>167608</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>50.77L</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>124.39</v>
+      </c>
+      <c r="H42" s="6" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="I42" s="6" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>15/10/26</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SAMPLE FUEL STATION B</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>716887</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>59.10L</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Unleaded</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>166.42</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="I36" s="6" t="n">
-        <v>-2</v>
-      </c>
-      <c r="J36" s="6" t="n">
-        <v>164.42</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>142.97</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>24/10/26</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>SAMPLE FUEL STATION C</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>159252</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>62.20L</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Unleaded</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>175.57</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="I37" s="6" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>503344</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>33.77L</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="I43" s="6" t="n">
         <v>-0</v>
       </c>
-      <c r="J37" s="6" t="n">
-        <v>175.57</v>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>152.67</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>18/10/26</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CARD FEE</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" s="6" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="6" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>30/10/26</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>TRANSACTION FEES</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" s="6" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" s="6" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Sub Totals</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="n">
-        <v>443.08</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="I40" s="7" t="n">
-        <v>-3.84</v>
-      </c>
-      <c r="J40" s="7" t="n">
-        <v>439.24</v>
-      </c>
-      <c r="K40" s="7" t="n">
-        <v>381.94</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>REGISTRATION: TST105</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>COST CENTRE:</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>CARD NO: 131676</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>DRIVER NAME:</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>Supplier Name</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Odometer Reading</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Voucher Number</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>Original Price Incl GST</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>GST</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Discount Value Incl GST</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Total Incl GST &amp; Discount</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>Total excl GST &amp; Incl Disc</t>
-        </is>
+      <c r="J43" s="6" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="K43" s="6" t="n">
+        <v>71.95</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06/10/26</t>
+          <t>25/10/26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SAMPLE FUEL STATION A</t>
+          <t>SAMPLE FUEL STATION D</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1907,12 +2003,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>244224</t>
+          <t>672214</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>48.30L</t>
+          <t>28.17L</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1921,30 +2017,30 @@
         </is>
       </c>
       <c r="G44" s="6" t="n">
-        <v>134.52</v>
+        <v>69.02</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>17.55</v>
+        <v>9</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>-0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>134.52</v>
+        <v>69.02</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>116.97</v>
+        <v>60.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>15/10/26</t>
+          <t>26/10/26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SAMPLE FUEL STATION B</t>
+          <t>SAMPLE FUEL STATION A</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1954,12 +2050,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>509520</t>
+          <t>521254</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>44.00L</t>
+          <t>31.34L</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1968,30 +2064,30 @@
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>124.3</v>
+        <v>76.78</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>16.21</v>
+        <v>10.01</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>-0</v>
+        <v>-0.92</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>124.3</v>
+        <v>75.86</v>
       </c>
       <c r="K45" s="6" t="n">
-        <v>108.09</v>
+        <v>65.97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>24/10/26</t>
+          <t>18/10/26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SAMPLE FUEL STATION C</t>
+          <t>CARD FEE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1999,46 +2095,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>276509</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>66.40L</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Diesel</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" s="6" t="n">
-        <v>187.09</v>
+        <v>4.59</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>24.4</v>
+        <v>0.6</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>187.09</v>
+        <v>4.59</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>162.69</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>18/10/26</t>
+          <t>30/10/26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CARD FEE</t>
+          <t>TRANSACTION FEES</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2054,7 +2142,7 @@
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" s="6" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0.6</v>
@@ -2063,168 +2151,176 @@
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>4.59</v>
+        <v>4.58</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>30/10/26</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>TRANSACTION FEES</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" s="6" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="H48" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="6" t="n">
-        <v>4.58</v>
-      </c>
-      <c r="K48" s="6" t="n">
-        <v>3.98</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Sub Totals</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
-        <v>455.08</v>
-      </c>
-      <c r="H49" s="7" t="n">
-        <v>59.36</v>
-      </c>
-      <c r="I49" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="7" t="n">
-        <v>455.08</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>395.72</v>
-      </c>
+      <c r="G48" s="7" t="n">
+        <v>433.22</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>-4.26</v>
+      </c>
+      <c r="J48" s="7" t="n">
+        <v>428.96</v>
+      </c>
+      <c r="K48" s="7" t="n">
+        <v>373.01</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRATION: TST105</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>COST CENTRE:</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>CARD NO: 131676</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>DRIVER NAME:</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>REGISTRATION: TST106</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>COST CENTRE:</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>CARD NO: 139595</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="3" t="inlineStr">
-        <is>
-          <t>DRIVER NAME:</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Supplier Name</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Odometer Reading</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Voucher Number</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>Original Price Incl GST</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Discount Value Incl GST</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Total Incl GST &amp; Discount</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>Total excl GST &amp; Incl Disc</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Supplier Name</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Odometer Reading</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Voucher Number</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>Original Price Incl GST</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>GST</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>Discount Value Incl GST</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>Total Incl GST &amp; Discount</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>Total excl GST &amp; Incl Disc</t>
-        </is>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>07/10/26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>939111</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>28.32L</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>69.38</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>67.98999999999999</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>59.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06/10/26</t>
+          <t>11/10/26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SAMPLE FUEL STATION A</t>
+          <t>SAMPLE FUEL STATION B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2234,44 +2330,44 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>440297</t>
+          <t>288743</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>63.20L</t>
+          <t>31.28L</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Unleaded</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="G53" s="6" t="n">
-        <v>176.54</v>
+        <v>76.64</v>
       </c>
       <c r="H53" s="6" t="n">
-        <v>23.03</v>
+        <v>10</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>-0</v>
+        <v>-0.92</v>
       </c>
       <c r="J53" s="6" t="n">
-        <v>176.54</v>
+        <v>75.72</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>153.51</v>
+        <v>65.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>15/10/26</t>
+          <t>13/10/26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SAMPLE FUEL STATION B</t>
+          <t>SAMPLE FUEL STATION C</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2281,44 +2377,44 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>594851</t>
+          <t>247568</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>34.20L</t>
+          <t>54.35L</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Unleaded</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
-        <v>96.68000000000001</v>
+        <v>133.16</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>12.61</v>
+        <v>17.37</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>-1.93</v>
+        <v>-2.66</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>94.75</v>
+        <v>130.5</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>82.39</v>
+        <v>113.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>24/10/26</t>
+          <t>23/10/26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAMPLE FUEL STATION C</t>
+          <t>SAMPLE FUEL STATION D</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2328,33 +2424,33 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>725035</t>
+          <t>530118</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>46.60L</t>
+          <t>22.44L</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Unleaded</t>
+          <t>Diesel</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
-        <v>130.5</v>
+        <v>54.98</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>17.02</v>
+        <v>7.17</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>-0</v>
+        <v>-0.66</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>130.5</v>
+        <v>54.32</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>113.48</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="56">
@@ -2442,19 +2538,1235 @@
         </is>
       </c>
       <c r="G58" s="7" t="n">
-        <v>412.89</v>
+        <v>343.33</v>
       </c>
       <c r="H58" s="7" t="n">
-        <v>53.86</v>
+        <v>44.79</v>
       </c>
       <c r="I58" s="7" t="n">
-        <v>-1.93</v>
+        <v>-5.63</v>
       </c>
       <c r="J58" s="7" t="n">
-        <v>410.96</v>
+        <v>337.7</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>357.35</v>
+        <v>293.64</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRATION: TST106</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>COST CENTRE:</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>CARD NO: 139595</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>DRIVER NAME:</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Supplier Name</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>Odometer Reading</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>Voucher Number</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>Original Price Incl GST</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Discount Value Incl GST</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Total Incl GST &amp; Discount</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>Total excl GST &amp; Incl Disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>01/10/26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>882712</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>38.18L</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="n">
+        <v>106.52</v>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>-2.13</v>
+      </c>
+      <c r="J62" s="6" t="n">
+        <v>104.39</v>
+      </c>
+      <c r="K62" s="6" t="n">
+        <v>90.77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16/10/26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION B</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>522479</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>17.55L</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>48.96</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>48.37</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>42.06</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>19/10/26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION C</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>931459</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>31.53L</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="n">
+        <v>87.97</v>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J64" s="6" t="n">
+        <v>87.97</v>
+      </c>
+      <c r="K64" s="6" t="n">
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>27/10/26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION D</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>247150</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>59.23L</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>165.25</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J65" s="6" t="n">
+        <v>165.25</v>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>143.7</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>28/10/26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>527781</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>31.60L</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="H66" s="6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J66" s="6" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>76.66</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>18/10/26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CARD FEE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>30/10/26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TRANSACTION FEES</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H68" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I68" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Sub Totals</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>506.03</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="J69" s="7" t="n">
+        <v>503.31</v>
+      </c>
+      <c r="K69" s="7" t="n">
+        <v>437.66</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRATION: TST107</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>COST CENTRE:</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>CARD NO: 147514</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>DRIVER NAME:</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>Supplier Name</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>Odometer Reading</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Voucher Number</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>Original Price Incl GST</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Discount Value Incl GST</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Total Incl GST &amp; Discount</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="inlineStr">
+        <is>
+          <t>Total excl GST &amp; Incl Disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>05/10/26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>235271</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>25.35L</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="I73" s="6" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="K73" s="6" t="n">
+        <v>52.93</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>06/10/26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION B</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>480232</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>34.64L</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="n">
+        <v>84.87</v>
+      </c>
+      <c r="H74" s="6" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="I74" s="6" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>83.17</v>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>72.31999999999999</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>17/10/26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION C</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>096527</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>26.30L</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="I75" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>64.44</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>56.03</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>21/10/26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION D</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>661451</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>29.99L</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="n">
+        <v>73.48</v>
+      </c>
+      <c r="H76" s="6" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="I76" s="6" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J76" s="6" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>63.13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>752201</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>28.81L</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Diesel</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>70.58</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="I77" s="6" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J77" s="6" t="n">
+        <v>70.58</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>61.37</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>18/10/26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>CARD FEE</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H78" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I78" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>30/10/26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TRANSACTION FEES</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K79" s="6" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Sub Totals</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>364.65</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="I80" s="7" t="n">
+        <v>-3.82</v>
+      </c>
+      <c r="J80" s="7" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="K80" s="7" t="n">
+        <v>313.75</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>REGISTRATION: TST108</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="n"/>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>COST CENTRE:</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="n"/>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>CARD NO: 155433</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>DRIVER NAME:</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="n"/>
+      <c r="I82" s="4" t="n"/>
+      <c r="J82" s="4" t="n"/>
+      <c r="K82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>Supplier Name</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Odometer Reading</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Voucher Number</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>Original Price Incl GST</t>
+        </is>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Discount Value Incl GST</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>Total Incl GST &amp; Discount</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="inlineStr">
+        <is>
+          <t>Total excl GST &amp; Incl Disc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>01/10/26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION A</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>594997</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>36.70L</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="H84" s="6" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="I84" s="6" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="J84" s="6" t="n">
+        <v>100.34</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>87.25</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>16/10/26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION B</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>420073</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>51.82L</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="n">
+        <v>144.58</v>
+      </c>
+      <c r="H85" s="6" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="I85" s="6" t="n">
+        <v>-1.73</v>
+      </c>
+      <c r="J85" s="6" t="n">
+        <v>142.85</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>124.22</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>25/10/26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION C</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>052767</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>35.11L</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="n">
+        <v>97.95999999999999</v>
+      </c>
+      <c r="H86" s="6" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="I86" s="6" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="J86" s="6" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>84.16</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>27/10/26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SAMPLE FUEL STATION D</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>649561</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>65.71L</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Unleaded</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="n">
+        <v>183.33</v>
+      </c>
+      <c r="H87" s="6" t="n">
+        <v>23.91</v>
+      </c>
+      <c r="I87" s="6" t="n">
+        <v>-3.67</v>
+      </c>
+      <c r="J87" s="6" t="n">
+        <v>179.66</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>156.23</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>18/10/26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>CARD FEE</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H88" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I88" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>30/10/26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TRANSACTION FEES</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="H89" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I89" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="6" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>3.98</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Sub Totals</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n">
+        <v>537.4299999999999</v>
+      </c>
+      <c r="H90" s="7" t="n">
+        <v>70.11</v>
+      </c>
+      <c r="I90" s="7" t="n">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="J90" s="7" t="n">
+        <v>528.8</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>459.83</v>
       </c>
     </row>
   </sheetData>
